--- a/www/flightdata/xlsx/eoss-304.xlsx
+++ b/www/flightdata/xlsx/eoss-304.xlsx
@@ -3891,7 +3891,7 @@
         <v>27549.65</v>
       </c>
       <c r="I2">
-        <v>696</v>
+        <v>512</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
